--- a/astro-site/public/dl/restaurant-financial-plan-templates/05-restaurant-pl-template-budget-vs-actual.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/05-restaurant-pl-template-budget-vs-actual.xlsx
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,6 +250,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -822,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B16"/>
+  <dimension ref="A2:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -913,6 +916,13 @@
       <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1008,13 +1018,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -1033,13 +1043,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -1058,13 +1068,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -1083,13 +1093,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -1108,15 +1118,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -1142,13 +1152,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -1167,13 +1177,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -1192,13 +1202,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -1217,13 +1227,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -1242,13 +1252,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -1267,13 +1277,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -1292,13 +1302,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -1317,13 +1327,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -1342,15 +1352,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -1358,7 +1368,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -1374,15 +1384,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -1390,7 +1400,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -1668,13 +1678,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -1693,13 +1703,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -1718,13 +1728,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -1743,13 +1753,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -1768,15 +1778,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -1802,13 +1812,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -1827,13 +1837,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -1852,13 +1862,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -1877,13 +1887,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -1902,13 +1912,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -1927,13 +1937,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -1952,13 +1962,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -1977,13 +1987,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -2002,15 +2012,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -2018,7 +2028,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -2034,15 +2044,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -2050,7 +2060,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -2328,13 +2338,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -2353,13 +2363,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -2378,13 +2388,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -2403,13 +2413,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -2428,15 +2438,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -2462,13 +2472,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -2487,13 +2497,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -2512,13 +2522,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -2537,13 +2547,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -2562,13 +2572,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -2587,13 +2597,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -2612,13 +2622,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -2637,13 +2647,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -2662,15 +2672,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -2678,7 +2688,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -2694,15 +2704,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -2710,7 +2720,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -2988,13 +2998,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -3013,13 +3023,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -3038,13 +3048,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -3063,13 +3073,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -3088,15 +3098,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -3122,13 +3132,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -3147,13 +3157,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -3172,13 +3182,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -3197,13 +3207,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -3222,13 +3232,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -3247,13 +3257,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -3272,13 +3282,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -3297,13 +3307,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -3322,15 +3332,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -3338,7 +3348,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -3354,15 +3364,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -3370,7 +3380,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -3689,55 +3699,55 @@
           <t>Total Revenue (Budget, excl. sales tax)</t>
         </is>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="37">
         <f>Jan!B10</f>
         <v>0.0</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="37">
         <f>Feb!B10</f>
         <v>0.0</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="37">
         <f>Mar!B10</f>
         <v>0.0</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="37">
         <f>Apr!B10</f>
         <v>0.0</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="37">
         <f>May!B10</f>
         <v>0.0</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="37">
         <f>Jun!B10</f>
         <v>0.0</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="37">
         <f>Jul!B10</f>
         <v>0.0</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="37">
         <f>Aug!B10</f>
         <v>0.0</v>
       </c>
-      <c r="J5" s="36">
+      <c r="J5" s="37">
         <f>Sep!B10</f>
         <v>0.0</v>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="37">
         <f>Oct!B10</f>
         <v>0.0</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="37">
         <f>Nov!B10</f>
         <v>0.0</v>
       </c>
-      <c r="M5" s="36">
+      <c r="M5" s="37">
         <f>Dec!B10</f>
         <v>0.0</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="37">
         <f>SUM(B5:M5)</f>
         <v>0.0</v>
       </c>
@@ -3748,55 +3758,55 @@
           <t>Total Revenue (Actual, excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="37">
         <f>Jan!C10</f>
         <v>0.0</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="37">
         <f>Feb!C10</f>
         <v>0.0</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="37">
         <f>Mar!C10</f>
         <v>0.0</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="37">
         <f>Apr!C10</f>
         <v>0.0</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="37">
         <f>May!C10</f>
         <v>0.0</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="37">
         <f>Jun!C10</f>
         <v>0.0</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="37">
         <f>Jul!C10</f>
         <v>0.0</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="37">
         <f>Aug!C10</f>
         <v>0.0</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="37">
         <f>Sep!C10</f>
         <v>0.0</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="37">
         <f>Oct!C10</f>
         <v>0.0</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="37">
         <f>Nov!C10</f>
         <v>0.0</v>
       </c>
-      <c r="M6" s="36">
+      <c r="M6" s="37">
         <f>Dec!C10</f>
         <v>0.0</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="37">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -3807,55 +3817,55 @@
           <t>Total Expenses (Budget)</t>
         </is>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="37">
         <f>Jan!B21</f>
         <v>0.0</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="37">
         <f>Feb!B21</f>
         <v>0.0</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="37">
         <f>Mar!B21</f>
         <v>0.0</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="37">
         <f>Apr!B21</f>
         <v>0.0</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="37">
         <f>May!B21</f>
         <v>0.0</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="37">
         <f>Jun!B21</f>
         <v>0.0</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="37">
         <f>Jul!B21</f>
         <v>0.0</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="37">
         <f>Aug!B21</f>
         <v>0.0</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="37">
         <f>Sep!B21</f>
         <v>0.0</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="37">
         <f>Oct!B21</f>
         <v>0.0</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="37">
         <f>Nov!B21</f>
         <v>0.0</v>
       </c>
-      <c r="M7" s="36">
+      <c r="M7" s="37">
         <f>Dec!B21</f>
         <v>0.0</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="37">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -3866,55 +3876,55 @@
           <t>Total Expenses (Actual)</t>
         </is>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <f>Jan!C21</f>
         <v>0.0</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>Feb!C21</f>
         <v>0.0</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="37">
         <f>Mar!C21</f>
         <v>0.0</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>Apr!C21</f>
         <v>0.0</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="37">
         <f>May!C21</f>
         <v>0.0</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="37">
         <f>Jun!C21</f>
         <v>0.0</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="37">
         <f>Jul!C21</f>
         <v>0.0</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="37">
         <f>Aug!C21</f>
         <v>0.0</v>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="37">
         <f>Sep!C21</f>
         <v>0.0</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="37">
         <f>Oct!C21</f>
         <v>0.0</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="37">
         <f>Nov!C21</f>
         <v>0.0</v>
       </c>
-      <c r="M8" s="36">
+      <c r="M8" s="37">
         <f>Dec!C21</f>
         <v>0.0</v>
       </c>
-      <c r="N8" s="36">
+      <c r="N8" s="37">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -3925,55 +3935,55 @@
           <t>EBITDA (Budget)</t>
         </is>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>Jan!B23</f>
         <v>0.0</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="37">
         <f>Feb!B23</f>
         <v>0.0</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="37">
         <f>Mar!B23</f>
         <v>0.0</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="37">
         <f>Apr!B23</f>
         <v>0.0</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="37">
         <f>May!B23</f>
         <v>0.0</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="37">
         <f>Jun!B23</f>
         <v>0.0</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="37">
         <f>Jul!B23</f>
         <v>0.0</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="37">
         <f>Aug!B23</f>
         <v>0.0</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="37">
         <f>Sep!B23</f>
         <v>0.0</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="37">
         <f>Oct!B23</f>
         <v>0.0</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="37">
         <f>Nov!B23</f>
         <v>0.0</v>
       </c>
-      <c r="M9" s="36">
+      <c r="M9" s="37">
         <f>Dec!B23</f>
         <v>0.0</v>
       </c>
-      <c r="N9" s="36">
+      <c r="N9" s="37">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -3984,55 +3994,55 @@
           <t>EBITDA (Actual)</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>Jan!C23</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>Feb!C23</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>Mar!C23</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>Apr!C23</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>May!C23</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>Jun!C23</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="37">
         <f>Jul!C23</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="37">
         <f>Aug!C23</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="36">
+      <c r="J10" s="37">
         <f>Sep!C23</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="37">
         <f>Oct!C23</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="37">
         <f>Nov!C23</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="36">
+      <c r="M10" s="37">
         <f>Dec!C23</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="36">
+      <c r="N10" s="37">
         <f>SUM(B10:M10)</f>
         <v>0.0</v>
       </c>
@@ -4043,55 +4053,55 @@
           <t>Revenue variance</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="38">
         <f>B6-B5</f>
         <v>0.0</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="38">
         <f>C6-C5</f>
         <v>0.0</v>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="38">
         <f>D6-D5</f>
         <v>0.0</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="38">
         <f>E6-E5</f>
         <v>0.0</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="38">
         <f>F6-F5</f>
         <v>0.0</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="38">
         <f>G6-G5</f>
         <v>0.0</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="38">
         <f>H6-H5</f>
         <v>0.0</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="38">
         <f>I6-I5</f>
         <v>0.0</v>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="38">
         <f>J6-J5</f>
         <v>0.0</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="38">
         <f>K6-K5</f>
         <v>0.0</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="38">
         <f>L6-L5</f>
         <v>0.0</v>
       </c>
-      <c r="M11" s="37">
+      <c r="M11" s="38">
         <f>M6-M5</f>
         <v>0.0</v>
       </c>
-      <c r="N11" s="36">
+      <c r="N11" s="37">
         <f>SUM(B11:M11)</f>
         <v>0.0</v>
       </c>
@@ -4161,55 +4171,55 @@
           <t>EBITDA variance</t>
         </is>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="38">
         <f>B10-B9</f>
         <v>0.0</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="38">
         <f>C10-C9</f>
         <v>0.0</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="38">
         <f>D10-D9</f>
         <v>0.0</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="38">
         <f>E10-E9</f>
         <v>0.0</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="38">
         <f>F10-F9</f>
         <v>0.0</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="38">
         <f>G10-G9</f>
         <v>0.0</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="38">
         <f>H10-H9</f>
         <v>0.0</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="38">
         <f>I10-I9</f>
         <v>0.0</v>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="38">
         <f>J10-J9</f>
         <v>0.0</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="38">
         <f>K10-K9</f>
         <v>0.0</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="38">
         <f>L10-L9</f>
         <v>0.0</v>
       </c>
-      <c r="M13" s="37">
+      <c r="M13" s="38">
         <f>M10-M9</f>
         <v>0.0</v>
       </c>
-      <c r="N13" s="36">
+      <c r="N13" s="37">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -4220,55 +4230,55 @@
           <t>Food cost (actual)</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>Jan!C13</f>
         <v>0.0</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>Feb!C13</f>
         <v>0.0</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>Mar!C13</f>
         <v>0.0</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>Apr!C13</f>
         <v>0.0</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>May!C13</f>
         <v>0.0</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>Jun!C13</f>
         <v>0.0</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>Jul!C13</f>
         <v>0.0</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>Aug!C13</f>
         <v>0.0</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="38">
         <f>Sep!C13</f>
         <v>0.0</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="38">
         <f>Oct!C13</f>
         <v>0.0</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>Nov!C13</f>
         <v>0.0</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>Dec!C13</f>
         <v>0.0</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="37">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -4279,55 +4289,55 @@
           <t>Beverage cost (actual)</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="38">
         <f>Jan!C14</f>
         <v>0.0</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>Feb!C14</f>
         <v>0.0</v>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f>Mar!C14</f>
         <v>0.0</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>Apr!C14</f>
         <v>0.0</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f>May!C14</f>
         <v>0.0</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="38">
         <f>Jun!C14</f>
         <v>0.0</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="38">
         <f>Jul!C14</f>
         <v>0.0</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="38">
         <f>Aug!C14</f>
         <v>0.0</v>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="38">
         <f>Sep!C14</f>
         <v>0.0</v>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="38">
         <f>Oct!C14</f>
         <v>0.0</v>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="38">
         <f>Nov!C14</f>
         <v>0.0</v>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="38">
         <f>Dec!C14</f>
         <v>0.0</v>
       </c>
-      <c r="N15" s="36">
+      <c r="N15" s="37">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -4338,55 +4348,55 @@
           <t>Labor (actual)</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="38">
         <f>Jan!C15</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <f>Feb!C15</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="38">
         <f>Mar!C15</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="38">
         <f>Apr!C15</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="38">
         <f>May!C15</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="38">
         <f>Jun!C15</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="38">
         <f>Jul!C15</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="38">
         <f>Aug!C15</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="38">
         <f>Sep!C15</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="38">
         <f>Oct!C15</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="38">
         <f>Nov!C15</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="37">
+      <c r="M16" s="38">
         <f>Dec!C15</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="37">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -4397,55 +4407,55 @@
           <t>Prime Cost (actual)</t>
         </is>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="38">
         <f>B14+B15+B16</f>
         <v>0.0</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="38">
         <f>C14+C15+C16</f>
         <v>0.0</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="38">
         <f>D14+D15+D16</f>
         <v>0.0</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="38">
         <f>E14+E15+E16</f>
         <v>0.0</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="38">
         <f>F14+F15+F16</f>
         <v>0.0</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="38">
         <f>G14+G15+G16</f>
         <v>0.0</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="38">
         <f>H14+H15+H16</f>
         <v>0.0</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="38">
         <f>I14+I15+I16</f>
         <v>0.0</v>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="38">
         <f>J14+J15+J16</f>
         <v>0.0</v>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="38">
         <f>K14+K15+K16</f>
         <v>0.0</v>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="38">
         <f>L14+L15+L16</f>
         <v>0.0</v>
       </c>
-      <c r="M17" s="37">
+      <c r="M17" s="38">
         <f>M14+M15+M16</f>
         <v>0.0</v>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="37">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -4671,13 +4681,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -4696,13 +4706,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -4721,13 +4731,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -4746,13 +4756,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -4771,15 +4781,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -4805,13 +4815,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -4830,13 +4840,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -4855,13 +4865,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -4880,13 +4890,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -4905,13 +4915,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -4930,13 +4940,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -4955,13 +4965,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -4980,13 +4990,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -5005,15 +5015,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -5021,7 +5031,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -5037,15 +5047,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -5053,7 +5063,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -5331,13 +5341,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -5356,13 +5366,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -5381,13 +5391,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -5406,13 +5416,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -5431,15 +5441,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -5465,13 +5475,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -5490,13 +5500,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -5515,13 +5525,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -5540,13 +5550,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -5565,13 +5575,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -5590,13 +5600,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -5615,13 +5625,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -5640,13 +5650,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -5665,15 +5675,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -5681,7 +5691,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -5697,15 +5707,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -5713,7 +5723,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -5991,13 +6001,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -6016,13 +6026,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -6041,13 +6051,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -6066,13 +6076,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -6091,15 +6101,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -6125,13 +6135,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -6150,13 +6160,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -6175,13 +6185,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -6200,13 +6210,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -6225,13 +6235,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -6250,13 +6260,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -6275,13 +6285,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -6300,13 +6310,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -6325,15 +6335,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -6341,7 +6351,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -6357,15 +6367,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -6373,7 +6383,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -6651,13 +6661,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -6676,13 +6686,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -6701,13 +6711,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -6726,13 +6736,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -6751,15 +6761,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -6785,13 +6795,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -6810,13 +6820,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -6835,13 +6845,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -6860,13 +6870,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -6885,13 +6895,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -6910,13 +6920,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -6935,13 +6945,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -6960,13 +6970,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -6985,15 +6995,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -7001,7 +7011,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -7017,15 +7027,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -7033,7 +7043,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -7311,13 +7321,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -7336,13 +7346,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -7361,13 +7371,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -7386,13 +7396,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -7411,15 +7421,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -7445,13 +7455,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -7470,13 +7480,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -7495,13 +7505,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -7520,13 +7530,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -7545,13 +7555,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -7570,13 +7580,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -7595,13 +7605,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -7620,13 +7630,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -7645,15 +7655,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -7661,7 +7671,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -7677,15 +7687,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -7693,7 +7703,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -7971,13 +7981,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -7996,13 +8006,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -8021,13 +8031,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -8046,13 +8056,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -8071,15 +8081,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -8105,13 +8115,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -8130,13 +8140,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -8155,13 +8165,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -8180,13 +8190,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -8205,13 +8215,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -8230,13 +8240,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -8255,13 +8265,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -8280,13 +8290,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -8305,15 +8315,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -8321,7 +8331,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -8337,15 +8347,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -8353,7 +8363,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -8631,13 +8641,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -8656,13 +8666,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -8681,13 +8691,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -8706,13 +8716,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -8731,15 +8741,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -8765,13 +8775,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -8790,13 +8800,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -8815,13 +8825,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -8840,13 +8850,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -8865,13 +8875,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -8890,13 +8900,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -8915,13 +8925,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -8940,13 +8950,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -8965,15 +8975,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -8981,7 +8991,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -8997,15 +9007,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -9013,7 +9023,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -9291,13 +9301,13 @@
           <t>Dine-in Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="33">
+      <c r="B6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <f>C6-B6</f>
         <v>0.0</v>
       </c>
@@ -9316,13 +9326,13 @@
           <t>Bar Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="33">
+      <c r="B7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
         <f>C7-B7</f>
         <v>0.0</v>
       </c>
@@ -9341,13 +9351,13 @@
           <t>Delivery Sales (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34">
         <f>C8-B8</f>
         <v>0.0</v>
       </c>
@@ -9366,13 +9376,13 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="33">
+      <c r="B9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34">
         <f>C9-B9</f>
         <v>0.0</v>
       </c>
@@ -9391,15 +9401,15 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>B6+B7+B8+B9</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>C6+C7+C8+C9</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <f>C10-B10</f>
         <v>0.0</v>
       </c>
@@ -9425,13 +9435,13 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="33">
+      <c r="B13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34">
         <f>C13-B13</f>
         <v>0.0</v>
       </c>
@@ -9450,13 +9460,13 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="33">
+      <c r="B14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="34">
         <f>C14-B14</f>
         <v>0.0</v>
       </c>
@@ -9475,13 +9485,13 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33">
+      <c r="B15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="34">
         <f>C15-B15</f>
         <v>0.0</v>
       </c>
@@ -9500,13 +9510,13 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="33">
+      <c r="B16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="34">
         <f>C16-B16</f>
         <v>0.0</v>
       </c>
@@ -9525,13 +9535,13 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="33">
+      <c r="B17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="34">
         <f>C17-B17</f>
         <v>0.0</v>
       </c>
@@ -9550,13 +9560,13 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="33">
+      <c r="B18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="34">
         <f>C18-B18</f>
         <v>0.0</v>
       </c>
@@ -9575,13 +9585,13 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="33">
+      <c r="B19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="34">
         <f>C19-B19</f>
         <v>0.0</v>
       </c>
@@ -9600,13 +9610,13 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="33">
+      <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="34">
         <f>C20-B20</f>
         <v>0.0</v>
       </c>
@@ -9625,15 +9635,15 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="35">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <f>C21-B21</f>
         <v>0.0</v>
       </c>
@@ -9641,7 +9651,7 @@
         <f>IF($B21=0,"",IFERROR(($C21-$B21)/$B21,""))</f>
         <v/>
       </c>
-      <c r="F21" s="34" t="str">
+      <c r="F21" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E21),IF($E21&lt;='Annual Summary'!$B$22,"✅ OK",IF($E21&lt;='Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
@@ -9657,15 +9667,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="35">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="35">
         <f>C23-B23</f>
         <v>0.0</v>
       </c>
@@ -9673,7 +9683,7 @@
         <f>IF($B23=0,"",IFERROR(($C23-$B23)/ABS($B23),""))</f>
         <v/>
       </c>
-      <c r="F23" s="34" t="str">
+      <c r="F23" s="35" t="str">
         <f>IFERROR(IF(ISNUMBER($E23),IF($E23&gt;=-'Annual Summary'!$B$22,"✅ OK",IF($E23&gt;=-'Annual Summary'!$B$23,"⚠️ Watch","🔴 Alert")),"—"),"—")</f>
         <v>—</v>
       </c>
